--- a/data/xlsx/bitac--cad-cam-design-and-programming-mechanical.xlsx
+++ b/data/xlsx/bitac--cad-cam-design-and-programming-mechanical.xlsx
@@ -646,7 +646,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -668,7 +670,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>10</v>
       </c>
@@ -690,7 +694,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -712,7 +718,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -734,7 +742,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -756,7 +766,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -778,7 +790,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -800,7 +814,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -822,7 +838,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
